--- a/data/trans_orig/IP07_C12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C12_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de cansancio para realizar lo que le gusta en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de haber estado demasiado cansado/a para disfrutar de las cosas que le gusta hacer, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3054</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3151</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2871</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5375</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4886</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5901</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>798</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40753</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35387</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45105</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,9%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24745</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20627</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28110</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41641</t>
+          <t>27312</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35760</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45649</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>66386</t>
+          <t>68065</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59585</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72566</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3640</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3765</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4093</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2596</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8476</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18532</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10875</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30932</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7730</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4263</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12676</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19357</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34998</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42878</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78698</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66206</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86902</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>43385</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38145</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>47709</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>80,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>78578</t>
+          <t>46553</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65290</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86417</t>
+          <t>50521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>121963</t>
+          <t>125250</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106288</t>
+          <t>111477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131620</t>
+          <t>134045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2179</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1895</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2770</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8049</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4512</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4014</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>833</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>8240</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2307</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13219</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6459</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24122</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>35316</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10691</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>58091</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>48,93%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>80,48%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24115</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>48189</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22667</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89567</t>
+          <t>38628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48766</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37777</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>56276</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>75,22%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>58,27%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>35305</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13827</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>59250</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>82,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>84581</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>71272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108971</t>
+          <t>93820</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,107 +2766,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6168</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5195</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4911</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4279</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2998</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10037</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>15616</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>11599</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>7016</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>17749</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>12336</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>7329</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>18249</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>21,69%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>33,19%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>10199</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>6387</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>16439</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>31285</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>43344</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>37558</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>48015</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>77,65%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>67,28%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>86,02%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>41319</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>35007</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>45952</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>77,26%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>65,45%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43821</t>
+          <t>44037</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36818</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>85140</t>
+          <t>87380</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>76844</t>
+          <t>78280</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92499</t>
+          <t>94461</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4765</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>47686</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>34801</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>65589</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>58708</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>32701</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>113487</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>53,92%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>106734</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>78553</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>178588</t>
+          <t>105456</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>211560</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>192651</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>225060</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>71,33%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>144753</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>93502</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>170004</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>68,78%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>44,42%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>80,77%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>213317</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>191787</t>
+          <t>143121</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>227517</t>
+          <t>164608</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>358070</t>
+          <t>365627</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>288306</t>
+          <t>343993</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>385157</t>
+          <t>384197</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
